--- a/outputs/01a17824-deaf-7751-918c-2543b1250eaf/压测交接表.xlsx
+++ b/outputs/01a17824-deaf-7751-918c-2543b1250eaf/压测交接表.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交接概览" sheetId="1" r:id="R27c97233a5b04030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="负载原理" sheetId="2" r:id="R64363084b2954fa7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitor用例" sheetId="3" r:id="Rf3cc5f00603346c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="七天计划" sheetId="4" r:id="Rf77881ea5b1c44e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日记录模板" sheetId="5" r:id="Rc2ec2d9a86714fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日志字段" sheetId="6" r:id="Rf96bb6eb2db1432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交接概览" sheetId="1" r:id="Rce2f2077beec43e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="负载原理" sheetId="2" r:id="Rf5da0c2db9354813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitor用例" sheetId="3" r:id="Rf282226c3a0f4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="压测方案" sheetId="4" r:id="Rfe6290e1d5f3428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运行记录模板" sheetId="5" r:id="R29ecba6884ab4a55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="日志字段" sheetId="6" r:id="R3ad30ff763d142f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -375,18 +375,18 @@
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="10" t="str">
-        <x:v>源码统一</x:v>
+        <x:v>操作流程</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>CPU/GPU 协议分支 5d6aca9 与 NPU 分支合并；集中入口 build.ps1/build.sh</x:v>
+        <x:v>三个模块沿用 validate/probe/pair/deploy/verify/run/collect/report</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="9" t="str">
-        <x:v>远端核对</x:v>
+        <x:v>运行入口</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>workload GitHub 已核对；Monitor GitHub 三次连接失败，保留本地已验证基线</x:v>
+        <x:v>使用 vmin_judge.exe；可选 stress 入口复用相同公共命令</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
@@ -399,7 +399,7 @@
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="9" t="str">
-        <x:v>七天记录</x:v>
+        <x:v>压测记录</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
         <x:v>下方汇总只链接人工录入的真实记录；空白不视为完成</x:v>
@@ -410,7 +410,7 @@
         <x:v>记录行数</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:f>IF(COUNTA('每日记录模板'!C5:C104)=0,"尚未填写",COUNTA('每日记录模板'!C5:C104))</x:f>
+        <x:f>IF(COUNTA('运行记录模板'!C5:C104)=0,"尚未填写",COUNTA('运行记录模板'!C5:C104))</x:f>
         <x:v>尚未填写</x:v>
       </x:c>
     </x:row>
@@ -419,7 +419,7 @@
         <x:v>输入的测量小时合计</x:v>
       </x:c>
       <x:c r="B11" s="19" t="str">
-        <x:f>IF(COUNT('每日记录模板'!E5:E104)=0,"尚无实测时长",SUM('每日记录模板'!E5:E104)/3600)</x:f>
+        <x:f>IF(COUNT('运行记录模板'!E5:E104)=0,"尚无实测时长",SUM('运行记录模板'!E5:E104)/3600)</x:f>
         <x:v>尚无实测时长</x:v>
       </x:c>
     </x:row>
@@ -428,7 +428,7 @@
         <x:v>操作入口</x:v>
       </x:c>
       <x:c r="B12" s="10" t="str">
-        <x:v>Monitor scripts/soak.py；先 dry-run，再按实际日期 run-day，最后 summarize</x:v>
+        <x:v>Monitor 可执行文件 stress；先 dry-run，再按实际阶段 run，最后 summarize</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
@@ -460,6 +460,7 @@
     <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="68" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="74" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -467,6 +468,7 @@
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
@@ -475,12 +477,14 @@
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
       <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1"/>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
       <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -495,8 +499,11 @@
       <x:c r="D4" s="7" t="str">
         <x:v>覆盖边界</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" ht="74" customHeight="1">
+      <x:c r="E4" s="7" t="str">
+        <x:v>本地源码路径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="120" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>cpu:integer</x:v>
       </x:c>
@@ -509,8 +516,11 @@
       <x:c r="D5" s="9" t="str">
         <x:v>主要观察整数执行路径；不保证特定指令端口或 NEON 覆盖。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" ht="74" customHeight="1">
+      <x:c r="E5" s="9" t="str">
+        <x:v>cpuworkload/src/backends/integer/integer_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="120" customHeight="1">
       <x:c r="A6" s="10" t="str">
         <x:v>cpu:floating_point</x:v>
       </x:c>
@@ -523,8 +533,11 @@
       <x:c r="D6" s="10" t="str">
         <x:v>编译器可优化代码，但没有显式承诺 SIMD/FMA 指令。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" ht="74" customHeight="1">
+      <x:c r="E6" s="10" t="str">
+        <x:v>cpuworkload/src/backends/floating_point/floating_point_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="120" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>cpu:matrix</x:v>
       </x:c>
@@ -537,8 +550,11 @@
       <x:c r="D7" s="9" t="str">
         <x:v>属于软件矩阵核，不等于专用矩阵指令或 NPU 负载。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" ht="74" customHeight="1">
+      <x:c r="E7" s="9" t="str">
+        <x:v>cpuworkload/src/backends/matrix/matrix_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="120" customHeight="1">
       <x:c r="A8" s="10" t="str">
         <x:v>cpu:memory</x:v>
       </x:c>
@@ -551,22 +567,28 @@
       <x:c r="D8" s="10" t="str">
         <x:v>改变工作集可改变缓存/内存压力；不是完整 DRAM 故障测试。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="74" customHeight="1">
+      <x:c r="E8" s="10" t="str">
+        <x:v>cpuworkload/src/backends/memory/memory_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="120" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>cpu:mixed</x:v>
       </x:c>
       <x:c r="B9" s="9" t="str">
-        <x:v>整数浮点矩阵内存混合</x:v>
+        <x:v>整数、浮点与随机访存混合</x:v>
       </x:c>
       <x:c r="C9" s="9" t="str">
-        <x:v>按混合后端组合执行多类确定性计算，提高多种路径的活动量。</x:v>
+        <x:v>同一循环交织整数递推、double 乘加与状态驱动的数组读改写；尾部合并数组样本与浮点位模式。</x:v>
       </x:c>
       <x:c r="D9" s="9" t="str">
-        <x:v>实际功耗与瓶颈需测量，名称不证明最大功耗。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="74" customHeight="1">
+        <x:v>不调用矩阵后端，不能代替独立 matrix 用例；不保证最大功耗。</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="str">
+        <x:v>cpuworkload/src/backends/mixed/mixed_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="120" customHeight="1">
       <x:c r="A10" s="10" t="str">
         <x:v>cpu:null</x:v>
       </x:c>
@@ -579,8 +601,11 @@
       <x:c r="D10" s="10" t="str">
         <x:v>不能作为持续计算压力或低功耗状态已进入的证明。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" ht="74" customHeight="1">
+      <x:c r="E10" s="10" t="str">
+        <x:v>cpuworkload/src/backends/null/null_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="120" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>gpu:alu</x:v>
       </x:c>
@@ -593,8 +618,11 @@
       <x:c r="D11" s="9" t="str">
         <x:v>Monitor Vulkan 配置使用 offscreen 图形路径。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12" ht="74" customHeight="1">
+      <x:c r="E11" s="9" t="str">
+        <x:v>gpuworkload/shaders/vulkan/workload.frag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="120" customHeight="1">
       <x:c r="A12" s="10" t="str">
         <x:v>gpu:sfu</x:v>
       </x:c>
@@ -607,8 +635,11 @@
       <x:c r="D12" s="10" t="str">
         <x:v>观察超越函数路径，不直接证明某个硬件 SFU 单元覆盖率。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13" ht="74" customHeight="1">
+      <x:c r="E12" s="10" t="str">
+        <x:v>gpuworkload/shaders/vulkan/workload.frag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="120" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>gpu:texture</x:v>
       </x:c>
@@ -621,8 +652,11 @@
       <x:c r="D13" s="9" t="str">
         <x:v>texture_count 在该实现中是重复采样倍率，不是独立纹理对象数。compute/OpenCL texture_like 不等同此路径。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="74" customHeight="1">
+      <x:c r="E13" s="9" t="str">
+        <x:v>gpuworkload/shaders/vulkan/workload.frag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="120" customHeight="1">
       <x:c r="A14" s="10" t="str">
         <x:v>gpu:fill</x:v>
       </x:c>
@@ -635,8 +669,11 @@
       <x:c r="D14" s="10" t="str">
         <x:v>该 shader 不使用 iterations；不能通过调 iterations 增强填充负载。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="74" customHeight="1">
+      <x:c r="E14" s="10" t="str">
+        <x:v>gpuworkload/shaders/vulkan/workload.frag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="120" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>gpu:mixed</x:v>
       </x:c>
@@ -649,8 +686,11 @@
       <x:c r="D15" s="9" t="str">
         <x:v>game_light/mid/heavy 是参数预设，不是实际游戏。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="74" customHeight="1">
+      <x:c r="E15" s="9" t="str">
+        <x:v>gpuworkload/shaders/vulkan/workload.frag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="120" customHeight="1">
       <x:c r="A16" s="10" t="str">
         <x:v>gpu:none</x:v>
       </x:c>
@@ -663,8 +703,11 @@
       <x:c r="D16" s="10" t="str">
         <x:v>Vulkan 实际后端不支持 idle/burst/分数占空比，不应宣称真实 GPU 休眠。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" ht="74" customHeight="1">
+      <x:c r="E16" s="10" t="str">
+        <x:v>gpuworkload/src/backends/null/null_backend.cpp</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="120" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>npu:kws01</x:v>
       </x:c>
@@ -677,8 +720,11 @@
       <x:c r="D17" s="9" t="str">
         <x:v>不含实时采音/MFCC 生成，不做关键词数据集准确率认证。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="74" customHeight="1">
+      <x:c r="E17" s="9" t="str">
+        <x:v>npuworkload/profiles/kws01/manifest.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="120" customHeight="1">
       <x:c r="A18" s="10" t="str">
         <x:v>npu:ic01</x:v>
       </x:c>
@@ -691,8 +737,11 @@
       <x:c r="D18" s="10" t="str">
         <x:v>输入为模型边界张量，不含摄像头/图像解码链路。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19" ht="74" customHeight="1">
+      <x:c r="E18" s="10" t="str">
+        <x:v>npuworkload/profiles/ic01/manifest.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="120" customHeight="1">
       <x:c r="A19" s="9" t="str">
         <x:v>npu:ad01</x:v>
       </x:c>
@@ -705,8 +754,11 @@
       <x:c r="D19" s="9" t="str">
         <x:v>没有独立计算数据集异常检测精度或阈值指标。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20" ht="74" customHeight="1">
+      <x:c r="E19" s="9" t="str">
+        <x:v>npuworkload/profiles/ad01/manifest.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="120" customHeight="1">
       <x:c r="A20" s="10" t="str">
         <x:v>npu:sww01</x:v>
       </x:c>
@@ -719,8 +771,11 @@
       <x:c r="D20" s="10" t="str">
         <x:v>不等于连续音频流的完整唤醒系统。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21" ht="74" customHeight="1">
+      <x:c r="E20" s="10" t="str">
+        <x:v>npuworkload/profiles/sww01/manifest.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="120" customHeight="1">
       <x:c r="A21" s="9" t="str">
         <x:v>npu:framework_smoke</x:v>
       </x:c>
@@ -732,6 +787,9 @@
       </x:c>
       <x:c r="D21" s="9" t="str">
         <x:v>不执行真实 NPU 模型，不能计入有效 NPU 压力时长。</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="str">
+        <x:v>npuworkload/profiles/framework_smoke/manifest.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -832,7 +890,7 @@
         <x:v>配置来源</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="74" customHeight="1">
+    <x:row r="5" ht="115" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>cpu_burst_qualification_kirin9030</x:v>
       </x:c>
@@ -840,7 +898,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
-        <x:v>整数浮点矩阵内存混合突发</x:v>
+        <x:v>整数浮点访存混合突发</x:v>
       </x:c>
       <x:c r="D5" s="9" t="str">
         <x:v>mixed</x:v>
@@ -867,7 +925,7 @@
         <x:v>config/workloads/cpu_burst_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="74" customHeight="1">
+    <x:row r="6" ht="115" customHeight="1">
       <x:c r="A6" s="10" t="str">
         <x:v>cpu_floating_point_qualification_kirin9030</x:v>
       </x:c>
@@ -902,7 +960,7 @@
         <x:v>config/workloads/cpu_floating_point_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="74" customHeight="1">
+    <x:row r="7" ht="115" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>cpu_idle_control_kirin9030</x:v>
       </x:c>
@@ -937,7 +995,7 @@
         <x:v>config/workloads/cpu_idle_control_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="74" customHeight="1">
+    <x:row r="8" ht="115" customHeight="1">
       <x:c r="A8" s="10" t="str">
         <x:v>cpu_integer_qualification_kirin9030</x:v>
       </x:c>
@@ -972,7 +1030,7 @@
         <x:v>config/workloads/cpu_integer_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="74" customHeight="1">
+    <x:row r="9" ht="115" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>cpu_matrix_qualification_kirin9030</x:v>
       </x:c>
@@ -1007,7 +1065,7 @@
         <x:v>config/workloads/cpu_matrix_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="74" customHeight="1">
+    <x:row r="10" ht="115" customHeight="1">
       <x:c r="A10" s="10" t="str">
         <x:v>cpu_memory_qualification_kirin9030</x:v>
       </x:c>
@@ -1042,7 +1100,7 @@
         <x:v>config/workloads/cpu_memory_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="74" customHeight="1">
+    <x:row r="11" ht="115" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>cpu_mixed_big4</x:v>
       </x:c>
@@ -1050,7 +1108,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C11" s="9" t="str">
-        <x:v>整数浮点矩阵内存混合</x:v>
+        <x:v>整数浮点访存混合</x:v>
       </x:c>
       <x:c r="D11" s="9" t="str">
         <x:v>mixed</x:v>
@@ -1077,7 +1135,7 @@
         <x:v>config/workloads/cpu_mixed_big4.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="74" customHeight="1">
+    <x:row r="12" ht="115" customHeight="1">
       <x:c r="A12" s="10" t="str">
         <x:v>cpu_qualification_kirin9030</x:v>
       </x:c>
@@ -1085,7 +1143,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C12" s="10" t="str">
-        <x:v>整数浮点矩阵内存混合</x:v>
+        <x:v>整数浮点访存混合</x:v>
       </x:c>
       <x:c r="D12" s="10" t="str">
         <x:v>mixed</x:v>
@@ -1112,7 +1170,7 @@
         <x:v>config/workloads/cpu_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="74" customHeight="1">
+    <x:row r="13" ht="115" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>cpu_smoke_kirin9030</x:v>
       </x:c>
@@ -1120,7 +1178,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C13" s="9" t="str">
-        <x:v>整数浮点矩阵内存混合</x:v>
+        <x:v>整数浮点访存混合</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
         <x:v>mixed</x:v>
@@ -1147,7 +1205,7 @@
         <x:v>config/workloads/cpu_smoke.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="74" customHeight="1">
+    <x:row r="14" ht="115" customHeight="1">
       <x:c r="A14" s="10" t="str">
         <x:v>cpu_stress_extreme_qualification_kirin9030</x:v>
       </x:c>
@@ -1155,7 +1213,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C14" s="10" t="str">
-        <x:v>整数浮点矩阵内存混合高强度</x:v>
+        <x:v>整数浮点访存混合高强度</x:v>
       </x:c>
       <x:c r="D14" s="10" t="str">
         <x:v>mixed</x:v>
@@ -1182,7 +1240,7 @@
         <x:v>config/workloads/cpu_stress_extreme_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="74" customHeight="1">
+    <x:row r="15" ht="115" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>cpu_stress_kirin9030</x:v>
       </x:c>
@@ -1190,7 +1248,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C15" s="9" t="str">
-        <x:v>整数浮点矩阵内存混合</x:v>
+        <x:v>整数浮点访存混合</x:v>
       </x:c>
       <x:c r="D15" s="9" t="str">
         <x:v>mixed</x:v>
@@ -1217,7 +1275,7 @@
         <x:v>config/workloads/cpu_stress.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="74" customHeight="1">
+    <x:row r="16" ht="115" customHeight="1">
       <x:c r="A16" s="10" t="str">
         <x:v>cpu_thermal_qualification_kirin9030</x:v>
       </x:c>
@@ -1225,7 +1283,7 @@
         <x:v>CPU</x:v>
       </x:c>
       <x:c r="C16" s="10" t="str">
-        <x:v>整数浮点矩阵内存混合持续升温</x:v>
+        <x:v>整数浮点访存混合持续升温</x:v>
       </x:c>
       <x:c r="D16" s="10" t="str">
         <x:v>mixed</x:v>
@@ -1252,7 +1310,7 @@
         <x:v>config/workloads/cpu_thermal_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="74" customHeight="1">
+    <x:row r="17" ht="115" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>gpu_alu_qualification_kirin9030</x:v>
       </x:c>
@@ -1287,7 +1345,7 @@
         <x:v>config/workloads/gpu_alu_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="74" customHeight="1">
+    <x:row r="18" ht="115" customHeight="1">
       <x:c r="A18" s="10" t="str">
         <x:v>gpu_fill_qualification_kirin9030</x:v>
       </x:c>
@@ -1322,7 +1380,7 @@
         <x:v>config/workloads/gpu_fill_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="74" customHeight="1">
+    <x:row r="19" ht="115" customHeight="1">
       <x:c r="A19" s="9" t="str">
         <x:v>gpu_load_heavy_kirin9030</x:v>
       </x:c>
@@ -1357,7 +1415,7 @@
         <x:v>config/workloads/gpu_load_heavy_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="74" customHeight="1">
+    <x:row r="20" ht="115" customHeight="1">
       <x:c r="A20" s="10" t="str">
         <x:v>gpu_load_light_kirin9030</x:v>
       </x:c>
@@ -1392,7 +1450,7 @@
         <x:v>config/workloads/gpu_load_light_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="74" customHeight="1">
+    <x:row r="21" ht="115" customHeight="1">
       <x:c r="A21" s="9" t="str">
         <x:v>gpu_load_mid_kirin9030</x:v>
       </x:c>
@@ -1427,7 +1485,7 @@
         <x:v>config/workloads/gpu_load_mid_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="74" customHeight="1">
+    <x:row r="22" ht="115" customHeight="1">
       <x:c r="A22" s="10" t="str">
         <x:v>gpu_qualification_kirin9030</x:v>
       </x:c>
@@ -1462,7 +1520,7 @@
         <x:v>config/workloads/gpu_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="74" customHeight="1">
+    <x:row r="23" ht="115" customHeight="1">
       <x:c r="A23" s="9" t="str">
         <x:v>gpu_sfu_qualification_kirin9030</x:v>
       </x:c>
@@ -1497,7 +1555,7 @@
         <x:v>config/workloads/gpu_sfu_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="74" customHeight="1">
+    <x:row r="24" ht="115" customHeight="1">
       <x:c r="A24" s="10" t="str">
         <x:v>gpu_smoke_kirin9030</x:v>
       </x:c>
@@ -1532,7 +1590,7 @@
         <x:v>config/workloads/gpu_smoke.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="74" customHeight="1">
+    <x:row r="25" ht="115" customHeight="1">
       <x:c r="A25" s="9" t="str">
         <x:v>gpu_stress_extreme_kirin9030</x:v>
       </x:c>
@@ -1567,7 +1625,7 @@
         <x:v>config/workloads/gpu_stress_extreme_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="74" customHeight="1">
+    <x:row r="26" ht="115" customHeight="1">
       <x:c r="A26" s="10" t="str">
         <x:v>gpu_stress_kirin9030</x:v>
       </x:c>
@@ -1602,7 +1660,7 @@
         <x:v>config/workloads/gpu_stress.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="74" customHeight="1">
+    <x:row r="27" ht="115" customHeight="1">
       <x:c r="A27" s="9" t="str">
         <x:v>gpu_texture_qualification_kirin9030</x:v>
       </x:c>
@@ -1637,7 +1695,7 @@
         <x:v>config/workloads/gpu_texture_qualification_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="74" customHeight="1">
+    <x:row r="28" ht="115" customHeight="1">
       <x:c r="A28" s="10" t="str">
         <x:v>gpu_thermal_kirin9030</x:v>
       </x:c>
@@ -1672,7 +1730,7 @@
         <x:v>config/workloads/gpu_thermal_kirin9030.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="74" customHeight="1">
+    <x:row r="29" ht="115" customHeight="1">
       <x:c r="A29" s="9" t="str">
         <x:v>gpu_vulkan_mixed</x:v>
       </x:c>
@@ -1707,7 +1765,7 @@
         <x:v>config/workloads/gpu_vulkan_mixed.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="74" customHeight="1">
+    <x:row r="30" ht="115" customHeight="1">
       <x:c r="A30" s="10" t="str">
         <x:v>npu_ad01_load</x:v>
       </x:c>
@@ -1742,7 +1800,7 @@
         <x:v>config/workloads/npu_ad01_load.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="74" customHeight="1">
+    <x:row r="31" ht="115" customHeight="1">
       <x:c r="A31" s="9" t="str">
         <x:v>npu_ad01_qualification</x:v>
       </x:c>
@@ -1777,7 +1835,7 @@
         <x:v>config/workloads/npu_ad01_qualification.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="74" customHeight="1">
+    <x:row r="32" ht="115" customHeight="1">
       <x:c r="A32" s="10" t="str">
         <x:v>npu_ad01_smoke</x:v>
       </x:c>
@@ -1812,7 +1870,7 @@
         <x:v>config/workloads/npu_ad01_smoke.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="74" customHeight="1">
+    <x:row r="33" ht="115" customHeight="1">
       <x:c r="A33" s="9" t="str">
         <x:v>npu_ic01_load</x:v>
       </x:c>
@@ -1847,7 +1905,7 @@
         <x:v>config/workloads/npu_ic01_load.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="74" customHeight="1">
+    <x:row r="34" ht="115" customHeight="1">
       <x:c r="A34" s="10" t="str">
         <x:v>npu_ic01_qualification</x:v>
       </x:c>
@@ -1882,7 +1940,7 @@
         <x:v>config/workloads/npu_ic01_qualification.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="74" customHeight="1">
+    <x:row r="35" ht="115" customHeight="1">
       <x:c r="A35" s="9" t="str">
         <x:v>npu_ic01_smoke</x:v>
       </x:c>
@@ -1917,7 +1975,7 @@
         <x:v>config/workloads/npu_ic01_smoke.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="74" customHeight="1">
+    <x:row r="36" ht="115" customHeight="1">
       <x:c r="A36" s="10" t="str">
         <x:v>npu_kws01_load</x:v>
       </x:c>
@@ -1952,7 +2010,7 @@
         <x:v>config/workloads/npu_kws01_load.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="74" customHeight="1">
+    <x:row r="37" ht="115" customHeight="1">
       <x:c r="A37" s="9" t="str">
         <x:v>npu_kws01_qualification</x:v>
       </x:c>
@@ -1987,7 +2045,7 @@
         <x:v>config/workloads/npu_kws01_qualification.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="74" customHeight="1">
+    <x:row r="38" ht="115" customHeight="1">
       <x:c r="A38" s="10" t="str">
         <x:v>npu_kws01_smoke</x:v>
       </x:c>
@@ -2022,7 +2080,7 @@
         <x:v>config/workloads/npu_kws01_smoke.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="74" customHeight="1">
+    <x:row r="39" ht="115" customHeight="1">
       <x:c r="A39" s="9" t="str">
         <x:v>npu_sww01_load</x:v>
       </x:c>
@@ -2057,7 +2115,7 @@
         <x:v>config/workloads/npu_sww01_load.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="74" customHeight="1">
+    <x:row r="40" ht="115" customHeight="1">
       <x:c r="A40" s="10" t="str">
         <x:v>npu_sww01_qualification</x:v>
       </x:c>
@@ -2092,7 +2150,7 @@
         <x:v>config/workloads/npu_sww01_qualification.json</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="74" customHeight="1">
+    <x:row r="41" ht="115" customHeight="1">
       <x:c r="A41" s="9" t="str">
         <x:v>npu_sww01_smoke</x:v>
       </x:c>
@@ -2158,7 +2216,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>七天用例运行计划</x:v>
+        <x:v>用例压测方案</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -2180,7 +2238,7 @@
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="7" t="str">
-        <x:v>天</x:v>
+        <x:v>阶段</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
         <x:v>重点</x:v>
@@ -3736,7 +3794,7 @@
         <x:v>build-manifest.json</x:v>
       </x:c>
       <x:c r="B5" s="9" t="str">
-        <x:v>target、源码/SDK/编译器、argv、退出码、产物 SHA</x:v>
+        <x:v>target、SDK/编译器、argv、退出码、产物 SHA</x:v>
       </x:c>
       <x:c r="C5" s="9" t="str">
         <x:v>host 不等于 ARM64；planned/failed 不算构建完成</x:v>
